--- a/org_predictor.xlsx
+++ b/org_predictor.xlsx
@@ -446,7 +446,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>H ($daf)</t>
+          <t>H (%daf)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -2049,7 +2049,9 @@
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C22" t="n">
         <v>33.4</v>
       </c>
@@ -2123,7 +2125,9 @@
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C23" t="n">
         <v>33.4</v>
       </c>
@@ -2197,7 +2201,9 @@
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C24" t="n">
         <v>33.4</v>
       </c>
@@ -2271,7 +2277,9 @@
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C25" t="n">
         <v>40.2</v>
       </c>
@@ -2345,7 +2353,9 @@
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C26" t="n">
         <v>40.2</v>
       </c>
@@ -9715,7 +9725,9 @@
       <c r="A123" s="1" t="n">
         <v>121</v>
       </c>
-      <c r="B123" t="inlineStr"/>
+      <c r="B123" t="n">
+        <v>3.5</v>
+      </c>
       <c r="C123" t="n">
         <v>14.22</v>
       </c>
@@ -9789,7 +9801,9 @@
       <c r="A124" s="1" t="n">
         <v>122</v>
       </c>
-      <c r="B124" t="inlineStr"/>
+      <c r="B124" t="n">
+        <v>3.5</v>
+      </c>
       <c r="C124" t="n">
         <v>14.22</v>
       </c>
@@ -9863,7 +9877,9 @@
       <c r="A125" s="1" t="n">
         <v>123</v>
       </c>
-      <c r="B125" t="inlineStr"/>
+      <c r="B125" t="n">
+        <v>3.5</v>
+      </c>
       <c r="C125" t="n">
         <v>14.22</v>
       </c>
@@ -9937,7 +9953,9 @@
       <c r="A126" s="1" t="n">
         <v>124</v>
       </c>
-      <c r="B126" t="inlineStr"/>
+      <c r="B126" t="n">
+        <v>3.5</v>
+      </c>
       <c r="C126" t="n">
         <v>14.22</v>
       </c>
@@ -10011,7 +10029,9 @@
       <c r="A127" s="1" t="n">
         <v>125</v>
       </c>
-      <c r="B127" t="inlineStr"/>
+      <c r="B127" t="n">
+        <v>3.5</v>
+      </c>
       <c r="C127" t="n">
         <v>14.22</v>
       </c>
@@ -10085,7 +10105,9 @@
       <c r="A128" s="1" t="n">
         <v>126</v>
       </c>
-      <c r="B128" t="inlineStr"/>
+      <c r="B128" t="n">
+        <v>3.5</v>
+      </c>
       <c r="C128" t="n">
         <v>14.22</v>
       </c>
@@ -10159,7 +10181,9 @@
       <c r="A129" s="1" t="n">
         <v>127</v>
       </c>
-      <c r="B129" t="inlineStr"/>
+      <c r="B129" t="n">
+        <v>3.5</v>
+      </c>
       <c r="C129" t="n">
         <v>14.22</v>
       </c>
@@ -10233,7 +10257,9 @@
       <c r="A130" s="1" t="n">
         <v>128</v>
       </c>
-      <c r="B130" t="inlineStr"/>
+      <c r="B130" t="n">
+        <v>3.5</v>
+      </c>
       <c r="C130" t="n">
         <v>14.22</v>
       </c>
@@ -10307,7 +10333,9 @@
       <c r="A131" s="1" t="n">
         <v>129</v>
       </c>
-      <c r="B131" t="inlineStr"/>
+      <c r="B131" t="n">
+        <v>3.5</v>
+      </c>
       <c r="C131" t="n">
         <v>14.22</v>
       </c>
@@ -10381,7 +10409,9 @@
       <c r="A132" s="1" t="n">
         <v>130</v>
       </c>
-      <c r="B132" t="inlineStr"/>
+      <c r="B132" t="n">
+        <v>3.5</v>
+      </c>
       <c r="C132" t="n">
         <v>14.83309326841631</v>
       </c>
@@ -10455,7 +10485,9 @@
       <c r="A133" s="1" t="n">
         <v>131</v>
       </c>
-      <c r="B133" t="inlineStr"/>
+      <c r="B133" t="n">
+        <v>3.5</v>
+      </c>
       <c r="C133" t="n">
         <v>14.83309326841631</v>
       </c>
@@ -10529,7 +10561,9 @@
       <c r="A134" s="1" t="n">
         <v>132</v>
       </c>
-      <c r="B134" t="inlineStr"/>
+      <c r="B134" t="n">
+        <v>3.5</v>
+      </c>
       <c r="C134" t="n">
         <v>14.83309326841631</v>
       </c>
@@ -10603,7 +10637,9 @@
       <c r="A135" s="1" t="n">
         <v>133</v>
       </c>
-      <c r="B135" t="inlineStr"/>
+      <c r="B135" t="n">
+        <v>3.5</v>
+      </c>
       <c r="C135" t="n">
         <v>14.83309326841631</v>
       </c>
@@ -10677,7 +10713,9 @@
       <c r="A136" s="1" t="n">
         <v>134</v>
       </c>
-      <c r="B136" t="inlineStr"/>
+      <c r="B136" t="n">
+        <v>3.5</v>
+      </c>
       <c r="C136" t="n">
         <v>14.83309326841631</v>
       </c>
@@ -10751,7 +10789,9 @@
       <c r="A137" s="1" t="n">
         <v>135</v>
       </c>
-      <c r="B137" t="inlineStr"/>
+      <c r="B137" t="n">
+        <v>3.5</v>
+      </c>
       <c r="C137" t="n">
         <v>14.83309326841631</v>
       </c>
@@ -10825,7 +10865,9 @@
       <c r="A138" s="1" t="n">
         <v>136</v>
       </c>
-      <c r="B138" t="inlineStr"/>
+      <c r="B138" t="n">
+        <v>3.5</v>
+      </c>
       <c r="C138" t="n">
         <v>14.83309326841631</v>
       </c>
@@ -10899,7 +10941,9 @@
       <c r="A139" s="1" t="n">
         <v>137</v>
       </c>
-      <c r="B139" t="inlineStr"/>
+      <c r="B139" t="n">
+        <v>3.5</v>
+      </c>
       <c r="C139" t="n">
         <v>14.83309326841631</v>
       </c>
@@ -15609,7 +15653,9 @@
       <c r="A201" s="1" t="n">
         <v>199</v>
       </c>
-      <c r="B201" t="inlineStr"/>
+      <c r="B201" t="n">
+        <v>3.5</v>
+      </c>
       <c r="C201" t="n">
         <v>15.61968196976115</v>
       </c>
@@ -15683,7 +15729,9 @@
       <c r="A202" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="B202" t="inlineStr"/>
+      <c r="B202" t="n">
+        <v>3.5</v>
+      </c>
       <c r="C202" t="n">
         <v>15.61968196976115</v>
       </c>
@@ -15757,7 +15805,9 @@
       <c r="A203" s="1" t="n">
         <v>201</v>
       </c>
-      <c r="B203" t="inlineStr"/>
+      <c r="B203" t="n">
+        <v>3.5</v>
+      </c>
       <c r="C203" t="n">
         <v>15.61968196976115</v>
       </c>
@@ -21151,7 +21201,9 @@
       <c r="A274" s="1" t="n">
         <v>272</v>
       </c>
-      <c r="B274" t="inlineStr"/>
+      <c r="B274" t="n">
+        <v>5</v>
+      </c>
       <c r="C274" t="n">
         <v>21.64705882352941</v>
       </c>
@@ -21225,7 +21277,9 @@
       <c r="A275" s="1" t="n">
         <v>273</v>
       </c>
-      <c r="B275" t="inlineStr"/>
+      <c r="B275" t="n">
+        <v>5</v>
+      </c>
       <c r="C275" t="n">
         <v>18.4</v>
       </c>
@@ -21299,7 +21353,9 @@
       <c r="A276" s="1" t="n">
         <v>274</v>
       </c>
-      <c r="B276" t="inlineStr"/>
+      <c r="B276" t="n">
+        <v>5</v>
+      </c>
       <c r="C276" t="n">
         <v>19.05882352941176</v>
       </c>
@@ -21373,7 +21429,9 @@
       <c r="A277" s="1" t="n">
         <v>275</v>
       </c>
-      <c r="B277" t="inlineStr"/>
+      <c r="B277" t="n">
+        <v>5</v>
+      </c>
       <c r="C277" t="n">
         <v>16.2</v>
       </c>
@@ -21447,7 +21505,9 @@
       <c r="A278" s="1" t="n">
         <v>276</v>
       </c>
-      <c r="B278" t="inlineStr"/>
+      <c r="B278" t="n">
+        <v>5</v>
+      </c>
       <c r="C278" t="n">
         <v>19.52941176470588</v>
       </c>
@@ -21521,7 +21581,9 @@
       <c r="A279" s="1" t="n">
         <v>277</v>
       </c>
-      <c r="B279" t="inlineStr"/>
+      <c r="B279" t="n">
+        <v>5</v>
+      </c>
       <c r="C279" t="n">
         <v>16.6</v>
       </c>
@@ -21595,7 +21657,9 @@
       <c r="A280" s="1" t="n">
         <v>278</v>
       </c>
-      <c r="B280" t="inlineStr"/>
+      <c r="B280" t="n">
+        <v>5</v>
+      </c>
       <c r="C280" t="n">
         <v>18.76470588235294</v>
       </c>
@@ -21669,7 +21733,9 @@
       <c r="A281" s="1" t="n">
         <v>279</v>
       </c>
-      <c r="B281" t="inlineStr"/>
+      <c r="B281" t="n">
+        <v>5</v>
+      </c>
       <c r="C281" t="n">
         <v>15.95</v>
       </c>
@@ -21743,7 +21809,9 @@
       <c r="A282" s="1" t="n">
         <v>280</v>
       </c>
-      <c r="B282" t="inlineStr"/>
+      <c r="B282" t="n">
+        <v>5</v>
+      </c>
       <c r="C282" t="n">
         <v>20.17647058823529</v>
       </c>
@@ -21817,7 +21885,9 @@
       <c r="A283" s="1" t="n">
         <v>281</v>
       </c>
-      <c r="B283" t="inlineStr"/>
+      <c r="B283" t="n">
+        <v>5</v>
+      </c>
       <c r="C283" t="n">
         <v>17.15</v>
       </c>
@@ -22803,7 +22873,9 @@
       <c r="A296" s="1" t="n">
         <v>294</v>
       </c>
-      <c r="B296" t="inlineStr"/>
+      <c r="B296" t="n">
+        <v>3.5</v>
+      </c>
       <c r="C296" t="n">
         <v>12.3004</v>
       </c>
@@ -22877,7 +22949,9 @@
       <c r="A297" s="1" t="n">
         <v>295</v>
       </c>
-      <c r="B297" t="inlineStr"/>
+      <c r="B297" t="n">
+        <v>3.5</v>
+      </c>
       <c r="C297" t="n">
         <v>12.3004</v>
       </c>
@@ -22951,7 +23025,9 @@
       <c r="A298" s="1" t="n">
         <v>296</v>
       </c>
-      <c r="B298" t="inlineStr"/>
+      <c r="B298" t="n">
+        <v>3.5</v>
+      </c>
       <c r="C298" t="n">
         <v>12.3004</v>
       </c>
@@ -23025,7 +23101,9 @@
       <c r="A299" s="1" t="n">
         <v>297</v>
       </c>
-      <c r="B299" t="inlineStr"/>
+      <c r="B299" t="n">
+        <v>3.5</v>
+      </c>
       <c r="C299" t="n">
         <v>12.3004</v>
       </c>
@@ -23403,7 +23481,9 @@
       <c r="A304" s="1" t="n">
         <v>302</v>
       </c>
-      <c r="B304" t="inlineStr"/>
+      <c r="B304" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C304" t="n">
         <v>18.6</v>
       </c>
@@ -23477,7 +23557,9 @@
       <c r="A305" s="1" t="n">
         <v>303</v>
       </c>
-      <c r="B305" t="inlineStr"/>
+      <c r="B305" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C305" t="n">
         <v>18.6</v>
       </c>
@@ -23551,7 +23633,9 @@
       <c r="A306" s="1" t="n">
         <v>304</v>
       </c>
-      <c r="B306" t="inlineStr"/>
+      <c r="B306" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C306" t="n">
         <v>18.6</v>
       </c>
@@ -25753,7 +25837,9 @@
       <c r="A335" s="1" t="n">
         <v>333</v>
       </c>
-      <c r="B335" t="inlineStr"/>
+      <c r="B335" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C335" t="n">
         <v>19.2</v>
       </c>
@@ -25827,7 +25913,9 @@
       <c r="A336" s="1" t="n">
         <v>334</v>
       </c>
-      <c r="B336" t="inlineStr"/>
+      <c r="B336" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C336" t="n">
         <v>20.4</v>
       </c>
@@ -25901,7 +25989,9 @@
       <c r="A337" s="1" t="n">
         <v>335</v>
       </c>
-      <c r="B337" t="inlineStr"/>
+      <c r="B337" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C337" t="n">
         <v>28.3</v>
       </c>
@@ -25975,7 +26065,9 @@
       <c r="A338" s="1" t="n">
         <v>336</v>
       </c>
-      <c r="B338" t="inlineStr"/>
+      <c r="B338" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C338" t="n">
         <v>19.7</v>
       </c>
@@ -26049,7 +26141,9 @@
       <c r="A339" s="1" t="n">
         <v>337</v>
       </c>
-      <c r="B339" t="inlineStr"/>
+      <c r="B339" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C339" t="n">
         <v>20.42</v>
       </c>
@@ -26123,7 +26217,9 @@
       <c r="A340" s="1" t="n">
         <v>338</v>
       </c>
-      <c r="B340" t="inlineStr"/>
+      <c r="B340" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C340" t="n">
         <v>20</v>
       </c>
@@ -26197,7 +26293,9 @@
       <c r="A341" s="1" t="n">
         <v>339</v>
       </c>
-      <c r="B341" t="inlineStr"/>
+      <c r="B341" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C341" t="n">
         <v>20.498</v>
       </c>
@@ -26271,7 +26369,9 @@
       <c r="A342" s="1" t="n">
         <v>340</v>
       </c>
-      <c r="B342" t="inlineStr"/>
+      <c r="B342" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C342" t="n">
         <v>16.95</v>
       </c>
@@ -26345,7 +26445,9 @@
       <c r="A343" s="1" t="n">
         <v>341</v>
       </c>
-      <c r="B343" t="inlineStr"/>
+      <c r="B343" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C343" t="n">
         <v>19.02</v>
       </c>
@@ -26419,7 +26521,9 @@
       <c r="A344" s="1" t="n">
         <v>342</v>
       </c>
-      <c r="B344" t="inlineStr"/>
+      <c r="B344" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C344" t="n">
         <v>19.3</v>
       </c>
@@ -26493,7 +26597,9 @@
       <c r="A345" s="1" t="n">
         <v>343</v>
       </c>
-      <c r="B345" t="inlineStr"/>
+      <c r="B345" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C345" t="n">
         <v>19.59</v>
       </c>
@@ -26567,7 +26673,9 @@
       <c r="A346" s="1" t="n">
         <v>344</v>
       </c>
-      <c r="B346" t="inlineStr"/>
+      <c r="B346" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C346" t="n">
         <v>20.008</v>
       </c>
@@ -26641,7 +26749,9 @@
       <c r="A347" s="1" t="n">
         <v>345</v>
       </c>
-      <c r="B347" t="inlineStr"/>
+      <c r="B347" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C347" t="n">
         <v>19.49</v>
       </c>
@@ -26715,7 +26825,9 @@
       <c r="A348" s="1" t="n">
         <v>346</v>
       </c>
-      <c r="B348" t="inlineStr"/>
+      <c r="B348" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C348" t="n">
         <v>16.6</v>
       </c>
@@ -26789,7 +26901,9 @@
       <c r="A349" s="1" t="n">
         <v>347</v>
       </c>
-      <c r="B349" t="inlineStr"/>
+      <c r="B349" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C349" t="n">
         <v>20.547</v>
       </c>
@@ -26863,7 +26977,9 @@
       <c r="A350" s="1" t="n">
         <v>348</v>
       </c>
-      <c r="B350" t="inlineStr"/>
+      <c r="B350" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C350" t="n">
         <v>18.99</v>
       </c>
@@ -26937,7 +27053,9 @@
       <c r="A351" s="1" t="n">
         <v>349</v>
       </c>
-      <c r="B351" t="inlineStr"/>
+      <c r="B351" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C351" t="n">
         <v>19</v>
       </c>
@@ -27011,7 +27129,9 @@
       <c r="A352" s="1" t="n">
         <v>350</v>
       </c>
-      <c r="B352" t="inlineStr"/>
+      <c r="B352" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C352" t="n">
         <v>19.849</v>
       </c>
@@ -27085,7 +27205,9 @@
       <c r="A353" s="1" t="n">
         <v>351</v>
       </c>
-      <c r="B353" t="inlineStr"/>
+      <c r="B353" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C353" t="n">
         <v>18.769</v>
       </c>
@@ -27159,7 +27281,9 @@
       <c r="A354" s="1" t="n">
         <v>352</v>
       </c>
-      <c r="B354" t="inlineStr"/>
+      <c r="B354" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C354" t="n">
         <v>20.257</v>
       </c>
@@ -27233,7 +27357,9 @@
       <c r="A355" s="1" t="n">
         <v>353</v>
       </c>
-      <c r="B355" t="inlineStr"/>
+      <c r="B355" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C355" t="n">
         <v>19</v>
       </c>
@@ -27307,7 +27433,9 @@
       <c r="A356" s="1" t="n">
         <v>354</v>
       </c>
-      <c r="B356" t="inlineStr"/>
+      <c r="B356" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C356" t="n">
         <v>19.777</v>
       </c>
@@ -27381,7 +27509,9 @@
       <c r="A357" s="1" t="n">
         <v>355</v>
       </c>
-      <c r="B357" t="inlineStr"/>
+      <c r="B357" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C357" t="n">
         <v>18.955</v>
       </c>
@@ -27455,7 +27585,9 @@
       <c r="A358" s="1" t="n">
         <v>356</v>
       </c>
-      <c r="B358" t="inlineStr"/>
+      <c r="B358" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C358" t="n">
         <v>20.78</v>
       </c>
@@ -27529,7 +27661,9 @@
       <c r="A359" s="1" t="n">
         <v>357</v>
       </c>
-      <c r="B359" t="inlineStr"/>
+      <c r="B359" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C359" t="n">
         <v>19.773</v>
       </c>
@@ -27603,7 +27737,9 @@
       <c r="A360" s="1" t="n">
         <v>358</v>
       </c>
-      <c r="B360" t="inlineStr"/>
+      <c r="B360" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C360" t="n">
         <v>18.89</v>
       </c>
@@ -27677,7 +27813,9 @@
       <c r="A361" s="1" t="n">
         <v>359</v>
       </c>
-      <c r="B361" t="inlineStr"/>
+      <c r="B361" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C361" t="n">
         <v>18.67</v>
       </c>
@@ -27751,7 +27889,9 @@
       <c r="A362" s="1" t="n">
         <v>360</v>
       </c>
-      <c r="B362" t="inlineStr"/>
+      <c r="B362" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C362" t="n">
         <v>18.261</v>
       </c>
@@ -27825,7 +27965,9 @@
       <c r="A363" s="1" t="n">
         <v>361</v>
       </c>
-      <c r="B363" t="inlineStr"/>
+      <c r="B363" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C363" t="n">
         <v>18.06</v>
       </c>
@@ -27899,7 +28041,9 @@
       <c r="A364" s="1" t="n">
         <v>362</v>
       </c>
-      <c r="B364" t="inlineStr"/>
+      <c r="B364" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C364" t="n">
         <v>18.41</v>
       </c>
@@ -27973,7 +28117,9 @@
       <c r="A365" s="1" t="n">
         <v>363</v>
       </c>
-      <c r="B365" t="inlineStr"/>
+      <c r="B365" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C365" t="n">
         <v>19.698</v>
       </c>
@@ -28047,7 +28193,9 @@
       <c r="A366" s="1" t="n">
         <v>364</v>
       </c>
-      <c r="B366" t="inlineStr"/>
+      <c r="B366" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C366" t="n">
         <v>19.17</v>
       </c>
@@ -28121,7 +28269,9 @@
       <c r="A367" s="1" t="n">
         <v>365</v>
       </c>
-      <c r="B367" t="inlineStr"/>
+      <c r="B367" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C367" t="n">
         <v>17.1</v>
       </c>
@@ -28195,7 +28345,9 @@
       <c r="A368" s="1" t="n">
         <v>366</v>
       </c>
-      <c r="B368" t="inlineStr"/>
+      <c r="B368" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C368" t="n">
         <v>18.64</v>
       </c>
@@ -28269,7 +28421,9 @@
       <c r="A369" s="1" t="n">
         <v>367</v>
       </c>
-      <c r="B369" t="inlineStr"/>
+      <c r="B369" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C369" t="n">
         <v>17</v>
       </c>
@@ -28343,7 +28497,9 @@
       <c r="A370" s="1" t="n">
         <v>368</v>
       </c>
-      <c r="B370" t="inlineStr"/>
+      <c r="B370" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C370" t="n">
         <v>18.73</v>
       </c>
@@ -28417,7 +28573,9 @@
       <c r="A371" s="1" t="n">
         <v>369</v>
       </c>
-      <c r="B371" t="inlineStr"/>
+      <c r="B371" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C371" t="n">
         <v>17.94</v>
       </c>
@@ -28491,7 +28649,9 @@
       <c r="A372" s="1" t="n">
         <v>370</v>
       </c>
-      <c r="B372" t="inlineStr"/>
+      <c r="B372" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C372" t="n">
         <v>18.047</v>
       </c>
@@ -28565,7 +28725,9 @@
       <c r="A373" s="1" t="n">
         <v>371</v>
       </c>
-      <c r="B373" t="inlineStr"/>
+      <c r="B373" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C373" t="n">
         <v>18.067</v>
       </c>
@@ -28639,7 +28801,9 @@
       <c r="A374" s="1" t="n">
         <v>372</v>
       </c>
-      <c r="B374" t="inlineStr"/>
+      <c r="B374" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C374" t="n">
         <v>17.988</v>
       </c>
@@ -28713,7 +28877,9 @@
       <c r="A375" s="1" t="n">
         <v>373</v>
       </c>
-      <c r="B375" t="inlineStr"/>
+      <c r="B375" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C375" t="n">
         <v>17.483</v>
       </c>
@@ -28787,7 +28953,9 @@
       <c r="A376" s="1" t="n">
         <v>374</v>
       </c>
-      <c r="B376" t="inlineStr"/>
+      <c r="B376" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C376" t="n">
         <v>17.951</v>
       </c>
@@ -28861,7 +29029,9 @@
       <c r="A377" s="1" t="n">
         <v>375</v>
       </c>
-      <c r="B377" t="inlineStr"/>
+      <c r="B377" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C377" t="n">
         <v>16.3</v>
       </c>
@@ -28935,7 +29105,9 @@
       <c r="A378" s="1" t="n">
         <v>376</v>
       </c>
-      <c r="B378" t="inlineStr"/>
+      <c r="B378" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C378" t="n">
         <v>15.206</v>
       </c>
@@ -29009,7 +29181,9 @@
       <c r="A379" s="1" t="n">
         <v>377</v>
       </c>
-      <c r="B379" t="inlineStr"/>
+      <c r="B379" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C379" t="n">
         <v>15.52</v>
       </c>
@@ -29083,7 +29257,9 @@
       <c r="A380" s="1" t="n">
         <v>378</v>
       </c>
-      <c r="B380" t="inlineStr"/>
+      <c r="B380" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C380" t="n">
         <v>15.29</v>
       </c>
@@ -29157,7 +29333,9 @@
       <c r="A381" s="1" t="n">
         <v>379</v>
       </c>
-      <c r="B381" t="inlineStr"/>
+      <c r="B381" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C381" t="n">
         <v>15.84</v>
       </c>
@@ -29231,7 +29409,9 @@
       <c r="A382" s="1" t="n">
         <v>380</v>
       </c>
-      <c r="B382" t="inlineStr"/>
+      <c r="B382" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C382" t="n">
         <v>15.09</v>
       </c>
@@ -29305,7 +29485,9 @@
       <c r="A383" s="1" t="n">
         <v>381</v>
       </c>
-      <c r="B383" t="inlineStr"/>
+      <c r="B383" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C383" t="n">
         <v>14.693</v>
       </c>
@@ -29379,7 +29561,9 @@
       <c r="A384" s="1" t="n">
         <v>382</v>
       </c>
-      <c r="B384" t="inlineStr"/>
+      <c r="B384" t="n">
+        <v>5.2</v>
+      </c>
       <c r="C384" t="n">
         <v>14.85</v>
       </c>
